--- a/quality/fixtures/member_data_sample.xlsx
+++ b/quality/fixtures/member_data_sample.xlsx
@@ -118,15 +118,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">XXXX</t>
+          <t xml:space="preserve">????</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Broken Unit Row</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9999999996</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">broken.unit@example.test</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XXXX</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t xml:space="preserve">DUMMY TEST SOCIETY LTD</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">rvistas</t>
         </is>
